--- a/artfynd/Lögdeälven käringberget artfynd.xlsx
+++ b/artfynd/Lögdeälven käringberget artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1988068</v>
+        <v>266906</v>
       </c>
       <c r="B2" t="n">
-        <v>80083</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>15 km V om Öreström, Ång</t>
+          <t>14 km SV om Västra Örtträsk, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>683124</v>
+        <v>682187</v>
       </c>
       <c r="R2" t="n">
-        <v>7106553</v>
+        <v>7107831</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2005-06-15</t>
+          <t>2005-06-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2005-06-15</t>
+          <t>2005-06-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1987249</v>
+        <v>389888</v>
       </c>
       <c r="B3" t="n">
-        <v>80083</v>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>14,1 km VSV om Provåker, Ång</t>
+          <t>14 km SV om Västra Örtträsk, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>684503</v>
+        <v>682187</v>
       </c>
       <c r="R3" t="n">
-        <v>7103461</v>
+        <v>7107831</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2005-06-04</t>
+          <t>2005-08-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2005-06-04</t>
+          <t>2005-08-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>62607507</v>
+        <v>267369</v>
       </c>
       <c r="B4" t="n">
-        <v>19902</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,58 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102001</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Urskogsvedfluga</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Xylophagus kowarzi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pleske, 1925)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>malaisefälla</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lögdeälven: Mossavattsbäckens utlopp, Ång</t>
+          <t>15 km V om Öreström, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>682916</v>
+        <v>683124</v>
       </c>
       <c r="R4" t="n">
-        <v>7106901</v>
+        <v>7106553</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -958,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-06-14</t>
+          <t>2005-07-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-07-02</t>
+          <t>2005-07-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,88 +950,64 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>sumpig blandskog med högörtveg. och bäverfällda lövträd</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>Sven Hellqvist</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>NHRS-SVHE 000015233</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sven Hellqvist</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sven Hellqvist, Niklas Johansson</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>70358826</v>
+        <v>1988068</v>
       </c>
       <c r="B5" t="n">
-        <v>79047</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>637</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
+          <t>15 km V om Öreström, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683268</v>
+        <v>683124</v>
       </c>
       <c r="R5" t="n">
-        <v>7106487</v>
+        <v>7106553</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2005-06-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2005-06-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,79 +1047,85 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>378079</v>
+        <v>62607509</v>
       </c>
       <c r="B6" t="n">
-        <v>91699</v>
+        <v>15084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>102100</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ravinspjutvingefluga</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lonchoptera nigrociliata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Duda, 1927</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>malaisefälla</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>13,7 km VSV om Provåker, Ång</t>
+          <t>Lögdeälven: Mossavattsbäckens utlopp, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685169</v>
+        <v>682916</v>
       </c>
       <c r="R6" t="n">
-        <v>7102592</v>
+        <v>7106901</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -1194,12 +1152,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2005-06-13</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2005-06-13</t>
+          <t>2016-07-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,26 +1168,41 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>sumpig blandskog med högörtveg. och bäverfällda lövträd</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>Sven Hellqvist</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>NHRS-SVHE 000015235</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Sven Hellqvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Sven Hellqvist, Niklas Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>15371638</v>
+        <v>62607536</v>
       </c>
       <c r="B7" t="n">
-        <v>30266</v>
+        <v>17734</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1237,26 +1210,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100840</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tallvägstekel</t>
-        </is>
+        <v>240427</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Deuteragenia vechti</t>
+          <t>Odinia xanthocera</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Day, 1979)</t>
+          <t>Collin, 1952</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1269,24 +1242,25 @@
           <t>hona</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>fönsterfälla</t>
+          <t>malaisefälla</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Käringberget, Ång</t>
+          <t>Lögdeälven: Mossavattsbäckens utlopp, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>684193</v>
+        <v>682916</v>
       </c>
       <c r="R7" t="n">
-        <v>7104417</v>
+        <v>7106901</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,27 +1284,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2012-06-01</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-07-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2012-08-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Sveaskog 8</t>
+          <t>2016-07-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,66 +1298,82 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>sumpig blandskog med högörtveg. och bäverfällda lövträd</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>Sven Hellqvist</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>NHRS-SVHE 000015268</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
+          <t>Sven Hellqvist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
+          <t>Sven Hellqvist, Niklas Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>84766758</v>
+        <v>267353</v>
       </c>
       <c r="B8" t="n">
-        <v>79047</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>637</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lögdeälven, 5 km uppströms väg 92, Ång</t>
+          <t>14 km VSV om Öreström, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>683310</v>
+        <v>683785</v>
       </c>
       <c r="R8" t="n">
-        <v>7106387</v>
+        <v>7105048</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,12 +1397,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
+          <t>2005-07-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
+          <t>2005-07-03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,22 +1417,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson, Aron Dynesius</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>84766757</v>
+        <v>70358822</v>
       </c>
       <c r="B9" t="n">
-        <v>79047</v>
+        <v>79394</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,17 +1457,26 @@
           <t>(L.) Ach.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lögdeälven, 5 km uppströms väg 92, Ång</t>
+          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>683282</v>
+        <v>683310</v>
       </c>
       <c r="R9" t="n">
-        <v>7106452</v>
+        <v>7106389</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,12 +1503,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,6 +1519,24 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1544,17 +1546,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson, Aron Dynesius</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>84766754</v>
+        <v>70358823</v>
       </c>
       <c r="B10" t="n">
-        <v>79047</v>
+        <v>79394</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,17 +1581,26 @@
           <t>(L.) Ach.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lögdeälven, 5 km uppströms väg 92, Ång</t>
+          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>683264</v>
+        <v>683272</v>
       </c>
       <c r="R10" t="n">
-        <v>7106486</v>
+        <v>7106494</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,12 +1627,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1632,6 +1643,24 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1641,64 +1670,64 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson, Aron Dynesius</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>26289615</v>
+        <v>70358824</v>
       </c>
       <c r="B11" t="n">
-        <v>58334</v>
+        <v>79394</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103044</v>
+        <v>637</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rivarliden,Lögdeälven, Ång</t>
+          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>684452</v>
+        <v>683267</v>
       </c>
       <c r="R11" t="n">
-        <v>7104071</v>
+        <v>7106503</v>
       </c>
       <c r="S11" t="n">
-        <v>270</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1722,22 +1751,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2007-05-27</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2007-05-27</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,73 +1767,91 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Per-Olof Nilsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Per-Olof Nilsson, Stefan Delin</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>48772363</v>
+        <v>70358825</v>
       </c>
       <c r="B12" t="n">
-        <v>57817</v>
+        <v>79394</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>637</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ormaggan, Käringbergets Ekopark, Ång</t>
+          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>683438</v>
+        <v>683269</v>
       </c>
       <c r="R12" t="n">
-        <v>7105998</v>
+        <v>7106489</v>
       </c>
       <c r="S12" t="n">
-        <v>270</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1838,22 +1875,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2014-03-23</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2014-03-23</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1864,73 +1891,91 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sven Jägbrant</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sven Jägbrant, André Ahlberg, Isak Vahlström, Jacob Rudhe</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20771767</v>
+        <v>70358826</v>
       </c>
       <c r="B13" t="n">
-        <v>56849</v>
+        <v>79394</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>637</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rivarliden,Lögdeälven, Ång</t>
+          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>684452</v>
+        <v>683268</v>
       </c>
       <c r="R13" t="n">
-        <v>7104071</v>
+        <v>7106487</v>
       </c>
       <c r="S13" t="n">
-        <v>270</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1954,22 +1999,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2005-05-08</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2005-05-08</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1980,26 +2015,44 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Per-Olof Nilsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Per-Olof Nilsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>70358836</v>
+        <v>70358827</v>
       </c>
       <c r="B14" t="n">
-        <v>79047</v>
+        <v>79394</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2040,10 +2093,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>683265</v>
+        <v>683279</v>
       </c>
       <c r="R14" t="n">
-        <v>7106481</v>
+        <v>7106493</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2120,57 +2173,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>26272961</v>
+        <v>70358828</v>
       </c>
       <c r="B15" t="n">
-        <v>57646</v>
+        <v>79394</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102119</v>
+        <v>637</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rivarliden,Lögdeälven, Ång</t>
+          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>684452</v>
+        <v>683280</v>
       </c>
       <c r="R15" t="n">
-        <v>7104071</v>
+        <v>7106483</v>
       </c>
       <c r="S15" t="n">
-        <v>270</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2194,22 +2247,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2007-05-27</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2007-05-27</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2220,72 +2263,91 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Per-Olof Nilsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Per-Olof Nilsson, Stefan Delin</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111769576</v>
+        <v>70358829</v>
       </c>
       <c r="B16" t="n">
-        <v>57761</v>
+        <v>79394</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>637</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Paradiset, Ång</t>
+          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>684427</v>
+        <v>683279</v>
       </c>
       <c r="R16" t="n">
-        <v>7103283</v>
+        <v>7106485</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2309,12 +2371,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2325,73 +2387,91 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Andreas Öster, kristina stenmarck</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
-        </is>
-      </c>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>14247467</v>
+        <v>70358830</v>
       </c>
       <c r="B17" t="n">
-        <v>5492</v>
+        <v>79394</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>101410</v>
+        <v>637</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>14 km VSV om Öreström, Ång</t>
+          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>683959</v>
+        <v>683265</v>
       </c>
       <c r="R17" t="n">
-        <v>7105861</v>
+        <v>7106482</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2415,22 +2495,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2005-08-29</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2005-08-29</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2441,26 +2511,44 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>70358838</v>
+        <v>70358831</v>
       </c>
       <c r="B18" t="n">
-        <v>79047</v>
+        <v>79394</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,7 +2575,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2501,10 +2589,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>683271</v>
+        <v>683270</v>
       </c>
       <c r="R18" t="n">
-        <v>7106481</v>
+        <v>7106483</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2581,10 +2669,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>70358846</v>
+        <v>70358832</v>
       </c>
       <c r="B19" t="n">
-        <v>79047</v>
+        <v>79394</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2611,7 +2699,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2625,10 +2713,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>683309</v>
+        <v>683270</v>
       </c>
       <c r="R19" t="n">
-        <v>7106405</v>
+        <v>7106480</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2705,10 +2793,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>84766756</v>
+        <v>70358833</v>
       </c>
       <c r="B20" t="n">
-        <v>79047</v>
+        <v>79394</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2733,17 +2821,26 @@
           <t>(L.) Ach.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lögdeälven, 5 km uppströms väg 92, Ång</t>
+          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>683259</v>
+        <v>683266</v>
       </c>
       <c r="R20" t="n">
-        <v>7106474</v>
+        <v>7106492</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2770,12 +2867,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2786,6 +2883,24 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2795,59 +2910,64 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson, Aron Dynesius</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>94726893</v>
+        <v>70358834</v>
       </c>
       <c r="B21" t="n">
-        <v>80083</v>
+        <v>79394</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>637</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Karlsbäck, Ång</t>
+          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>684890</v>
+        <v>683258</v>
       </c>
       <c r="R21" t="n">
-        <v>7103649</v>
+        <v>7106482</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2871,17 +2991,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs inventering.</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2892,26 +3007,44 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>70358841</v>
+        <v>70358835</v>
       </c>
       <c r="B22" t="n">
-        <v>79047</v>
+        <v>79394</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2938,7 +3071,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2952,10 +3085,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>683279</v>
+        <v>683261</v>
       </c>
       <c r="R22" t="n">
-        <v>7106466</v>
+        <v>7106484</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3001,12 +3134,12 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AN22" t="n">
@@ -3014,7 +3147,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>1 substratenheter # Picea abies</t>
+          <t>1 substratenheter # Betula</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3032,10 +3165,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>70358832</v>
+        <v>70358836</v>
       </c>
       <c r="B23" t="n">
-        <v>79047</v>
+        <v>79394</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3062,7 +3195,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3076,10 +3209,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>683270</v>
+        <v>683265</v>
       </c>
       <c r="R23" t="n">
-        <v>7106480</v>
+        <v>7106481</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3156,48 +3289,57 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>389888</v>
+        <v>70358837</v>
       </c>
       <c r="B24" t="n">
-        <v>82792</v>
+        <v>79394</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>637</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>14 km SV om Västra Örtträsk, Ång</t>
+          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>682187</v>
+        <v>683265</v>
       </c>
       <c r="R24" t="n">
-        <v>7107831</v>
+        <v>7106480</v>
       </c>
       <c r="S24" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3221,12 +3363,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2005-08-18</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2005-08-18</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3237,64 +3379,91 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1992352</v>
+        <v>70358838</v>
       </c>
       <c r="B25" t="n">
-        <v>80083</v>
+        <v>79394</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>637</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>14 km VSV om Öreström, Ång</t>
+          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>684241</v>
+        <v>683271</v>
       </c>
       <c r="R25" t="n">
-        <v>7104295</v>
+        <v>7106481</v>
       </c>
       <c r="S25" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3318,12 +3487,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2005-08-25</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2005-08-25</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3334,68 +3503,91 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>23724050</v>
+        <v>70358839</v>
       </c>
       <c r="B26" t="n">
-        <v>57069</v>
+        <v>79394</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102954</v>
+        <v>637</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rivarliden,Lögdeälven, Ång</t>
+          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>684452</v>
+        <v>683272</v>
       </c>
       <c r="R26" t="n">
-        <v>7104071</v>
+        <v>7106477</v>
       </c>
       <c r="S26" t="n">
-        <v>270</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3419,22 +3611,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2006-05-20</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2006-05-20</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3445,26 +3627,44 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Per-Olof Nilsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Per-Olof Nilsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>70358837</v>
+        <v>70358840</v>
       </c>
       <c r="B27" t="n">
-        <v>79047</v>
+        <v>79394</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3491,7 +3691,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3505,10 +3705,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>683265</v>
+        <v>683270</v>
       </c>
       <c r="R27" t="n">
-        <v>7106480</v>
+        <v>7106478</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3585,10 +3785,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>70358833</v>
+        <v>70358841</v>
       </c>
       <c r="B28" t="n">
-        <v>79047</v>
+        <v>79394</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3615,7 +3815,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3629,10 +3829,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>683266</v>
+        <v>683279</v>
       </c>
       <c r="R28" t="n">
-        <v>7106492</v>
+        <v>7106466</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3709,10 +3909,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>70358835</v>
+        <v>70358842</v>
       </c>
       <c r="B29" t="n">
-        <v>79047</v>
+        <v>79394</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3739,7 +3939,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3753,10 +3953,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>683261</v>
+        <v>683284</v>
       </c>
       <c r="R29" t="n">
-        <v>7106484</v>
+        <v>7106458</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3802,12 +4002,12 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AN29" t="n">
@@ -3815,7 +4015,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>1 substratenheter # Betula</t>
+          <t>1 substratenheter # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3833,48 +4033,57 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>103410953</v>
+        <v>70358844</v>
       </c>
       <c r="B30" t="n">
-        <v>92535</v>
+        <v>79394</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>637</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Karlsbäck, Ång</t>
+          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>683864</v>
+        <v>683285</v>
       </c>
       <c r="R30" t="n">
-        <v>7105319</v>
+        <v>7106449</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3898,17 +4107,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3919,64 +4123,91 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>2 substratenheter # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>95135</v>
+        <v>70358846</v>
       </c>
       <c r="B31" t="n">
-        <v>78647</v>
+        <v>79394</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>637</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>14 km V om Öreström, Ång</t>
+          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>683893</v>
+        <v>683309</v>
       </c>
       <c r="R31" t="n">
-        <v>7106501</v>
+        <v>7106405</v>
       </c>
       <c r="S31" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4000,12 +4231,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2005-07-06</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2005-07-06</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4016,73 +4247,82 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>48755362</v>
+        <v>84766747</v>
       </c>
       <c r="B32" t="n">
-        <v>58027</v>
+        <v>79394</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>637</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ormaggan, Käringbergets Ekopark, Ång</t>
+          <t>Lögdeälven, 5 km uppströms väg 92, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>683438</v>
+        <v>683262</v>
       </c>
       <c r="R32" t="n">
-        <v>7105998</v>
+        <v>7106503</v>
       </c>
       <c r="S32" t="n">
-        <v>270</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4106,22 +4346,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2014-03-23</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2014-03-23</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4136,22 +4366,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sven Jägbrant</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sven Jägbrant, Jacob Rudhe, Isak Vahlström, André Ahlberg</t>
+          <t>Isak Vahlström, Carl Jansson, Aron Dynesius</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>70358825</v>
+        <v>84766748</v>
       </c>
       <c r="B33" t="n">
-        <v>79047</v>
+        <v>79394</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4176,26 +4406,17 @@
           <t>(L.) Ach.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
+          <t>Lögdeälven, 5 km uppströms väg 92, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>683269</v>
+        <v>683264</v>
       </c>
       <c r="R33" t="n">
-        <v>7106489</v>
+        <v>7106486</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4222,12 +4443,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4238,24 +4459,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4265,17 +4468,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Carl Jansson, Aron Dynesius</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>48754881</v>
+        <v>84766749</v>
       </c>
       <c r="B34" t="n">
-        <v>57023</v>
+        <v>79394</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4283,46 +4486,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102952</v>
+        <v>637</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Vanellus vanellus</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>sträckande</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ormaggan, Käringbergets Ekopark, Ång</t>
+          <t>Lögdeälven, 5 km uppströms väg 92, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>683438</v>
+        <v>683262</v>
       </c>
       <c r="R34" t="n">
-        <v>7105998</v>
+        <v>7106491</v>
       </c>
       <c r="S34" t="n">
-        <v>270</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4346,22 +4540,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2014-03-23</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2014-03-23</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4376,22 +4560,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Sven Jägbrant</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sven Jägbrant, Jacob Rudhe, André Ahlberg, Isak Vahlström</t>
+          <t>Isak Vahlström, Carl Jansson, Aron Dynesius</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>70358827</v>
+        <v>84766750</v>
       </c>
       <c r="B35" t="n">
-        <v>79047</v>
+        <v>79394</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4416,26 +4600,17 @@
           <t>(L.) Ach.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
+          <t>Lögdeälven, 5 km uppströms väg 92, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>683279</v>
+        <v>683265</v>
       </c>
       <c r="R35" t="n">
-        <v>7106493</v>
+        <v>7106489</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4462,12 +4637,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4478,24 +4653,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4505,17 +4662,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Carl Jansson, Aron Dynesius</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>70358840</v>
+        <v>84766751</v>
       </c>
       <c r="B36" t="n">
-        <v>79047</v>
+        <v>79394</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4540,26 +4697,17 @@
           <t>(L.) Ach.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
+          <t>Lögdeälven, 5 km uppströms väg 92, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>683270</v>
+        <v>683264</v>
       </c>
       <c r="R36" t="n">
-        <v>7106478</v>
+        <v>7106487</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4586,12 +4734,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4602,24 +4750,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4629,17 +4759,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Carl Jansson, Aron Dynesius</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>70358829</v>
+        <v>84766752</v>
       </c>
       <c r="B37" t="n">
-        <v>79047</v>
+        <v>79394</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,26 +4794,17 @@
           <t>(L.) Ach.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
+          <t>Lögdeälven, 5 km uppströms väg 92, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>683279</v>
+        <v>683275</v>
       </c>
       <c r="R37" t="n">
-        <v>7106485</v>
+        <v>7106480</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4710,12 +4831,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4726,24 +4847,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4753,17 +4856,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Carl Jansson, Aron Dynesius</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>70358844</v>
+        <v>84766756</v>
       </c>
       <c r="B38" t="n">
-        <v>79047</v>
+        <v>79394</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4788,26 +4891,17 @@
           <t>(L.) Ach.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
+          <t>Lögdeälven, 5 km uppströms väg 92, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>683285</v>
+        <v>683259</v>
       </c>
       <c r="R38" t="n">
-        <v>7106449</v>
+        <v>7106474</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4834,12 +4928,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4850,24 +4944,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>2 substratenheter # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4877,17 +4953,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Carl Jansson, Aron Dynesius</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>70358824</v>
+        <v>84766757</v>
       </c>
       <c r="B39" t="n">
-        <v>79047</v>
+        <v>79394</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4912,26 +4988,17 @@
           <t>(L.) Ach.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
+          <t>Lögdeälven, 5 km uppströms väg 92, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>683267</v>
+        <v>683282</v>
       </c>
       <c r="R39" t="n">
-        <v>7106503</v>
+        <v>7106452</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4958,12 +5025,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4974,24 +5041,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5001,59 +5050,55 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Carl Jansson, Aron Dynesius</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>84302339</v>
+        <v>84766758</v>
       </c>
       <c r="B40" t="n">
-        <v>58027</v>
+        <v>79394</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103015</v>
+        <v>637</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ormaggan, Stor-Lögdeåberget, Ång</t>
+          <t>Lögdeälven, 5 km uppströms väg 92, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>683554</v>
+        <v>683310</v>
       </c>
       <c r="R40" t="n">
-        <v>7106142</v>
+        <v>7106387</v>
       </c>
       <c r="S40" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5077,22 +5122,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2020-04-10</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2020-04-10</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5107,57 +5142,65 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Antoine Bos</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Antoine Bos, Andreas Bernhold</t>
+          <t>Isak Vahlström, Carl Jansson, Aron Dynesius</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>294955</v>
+        <v>84302328</v>
       </c>
       <c r="B41" t="n">
-        <v>91832</v>
+        <v>57950</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1179</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>14 km V om Öreström, Ång</t>
+          <t>Ormaggan, Stor-Lögdeåberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>683893</v>
+        <v>683554</v>
       </c>
       <c r="R41" t="n">
-        <v>7106501</v>
+        <v>7106142</v>
       </c>
       <c r="S41" t="n">
         <v>100</v>
@@ -5184,12 +5227,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2005-06-07</t>
+          <t>2020-04-10</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2005-06-07</t>
+          <t>2020-04-10</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5204,60 +5257,64 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Antoine Bos</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Antoine Bos, Andreas Bernhold</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>84766749</v>
+        <v>84302339</v>
       </c>
       <c r="B42" t="n">
-        <v>79047</v>
+        <v>58327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>637</v>
+        <v>103015</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lögdeälven, 5 km uppströms väg 92, Ång</t>
+          <t>Ormaggan, Stor-Lögdeåberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>683262</v>
+        <v>683554</v>
       </c>
       <c r="R42" t="n">
-        <v>7106491</v>
+        <v>7106142</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5281,12 +5338,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
+          <t>2020-04-10</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
+          <t>2020-04-10</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5301,57 +5368,66 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Antoine Bos</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson, Aron Dynesius</t>
+          <t>Antoine Bos, Andreas Bernhold</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>84766752</v>
+        <v>70305972</v>
       </c>
       <c r="B43" t="n">
-        <v>79047</v>
+        <v>56689</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>637</v>
+        <v>206046</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lögdeälven, 5 km uppströms väg 92, Ång</t>
+          <t>Käringberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>683275</v>
+        <v>683563</v>
       </c>
       <c r="R43" t="n">
-        <v>7106480</v>
+        <v>7106228</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5378,12 +5454,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
+          <t>2018-03-30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
+          <t>2018-03-30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5403,17 +5479,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson, Aron Dynesius</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>95137</v>
+        <v>1992352</v>
       </c>
       <c r="B44" t="n">
-        <v>78647</v>
+        <v>80432</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5421,21 +5497,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5445,10 +5521,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>683868</v>
+        <v>684241</v>
       </c>
       <c r="R44" t="n">
-        <v>7106045</v>
+        <v>7104295</v>
       </c>
       <c r="S44" t="n">
         <v>100</v>
@@ -5475,12 +5551,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2005-07-07</t>
+          <t>2005-08-25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2005-07-07</t>
+          <t>2005-08-25</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5495,69 +5571,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>70358822</v>
+        <v>103410953</v>
       </c>
       <c r="B45" t="n">
-        <v>79047</v>
+        <v>93197</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>637</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
+          <t>Karlsbäck, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>683310</v>
+        <v>683864</v>
       </c>
       <c r="R45" t="n">
-        <v>7106389</v>
+        <v>7105319</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5581,12 +5648,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5597,91 +5669,64 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>70358831</v>
+        <v>103410782</v>
       </c>
       <c r="B46" t="n">
-        <v>79047</v>
+        <v>93209</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>637</v>
+        <v>4366</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
+          <t>Karlsbäck, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>683270</v>
+        <v>683860</v>
       </c>
       <c r="R46" t="n">
-        <v>7106483</v>
+        <v>7105273</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5705,12 +5750,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5721,82 +5771,64 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>84766750</v>
+        <v>85601</v>
       </c>
       <c r="B47" t="n">
-        <v>79047</v>
+        <v>97358</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>637</v>
+        <v>53</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lögdeälven, 5 km uppströms väg 92, Ång</t>
+          <t>14 km V om Öreström, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>683265</v>
+        <v>683893</v>
       </c>
       <c r="R47" t="n">
-        <v>7106489</v>
+        <v>7106501</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5820,12 +5852,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
+          <t>2005-06-16</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
+          <t>2005-06-16</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5840,63 +5872,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson, Aron Dynesius</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>111769654</v>
+        <v>95135</v>
       </c>
       <c r="B48" t="n">
-        <v>90001</v>
+        <v>78993</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Paradiset, Ång</t>
+          <t>14 km V om Öreström, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>684522</v>
+        <v>683893</v>
       </c>
       <c r="R48" t="n">
-        <v>7103109</v>
+        <v>7106501</v>
       </c>
       <c r="S48" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5920,12 +5949,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2005-07-06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2005-07-06</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5934,29 +5963,28 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Andreas Öster, kristina stenmarck</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48772409</v>
+        <v>95137</v>
       </c>
       <c r="B49" t="n">
-        <v>57654</v>
+        <v>78993</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5964,46 +5992,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ormaggan, Käringbergets Ekopark, Ång</t>
+          <t>14 km VSV om Öreström, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>683438</v>
+        <v>683868</v>
       </c>
       <c r="R49" t="n">
-        <v>7105998</v>
+        <v>7106045</v>
       </c>
       <c r="S49" t="n">
-        <v>270</v>
+        <v>100</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6027,22 +6046,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2014-03-23</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2005-07-07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2014-03-23</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2005-07-07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6057,22 +6066,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Sven Jägbrant</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Sven Jägbrant, André Ahlberg, Isak Vahlström, Jacob Rudhe</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>70358839</v>
+        <v>294955</v>
       </c>
       <c r="B50" t="n">
-        <v>79047</v>
+        <v>92522</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6080,46 +6089,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>637</v>
+        <v>1179</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Peck) Donk</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
+          <t>14 km V om Öreström, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>683272</v>
+        <v>683893</v>
       </c>
       <c r="R50" t="n">
-        <v>7106477</v>
+        <v>7106501</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6143,12 +6143,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2005-06-07</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2005-06-07</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6159,91 +6159,69 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>23723936</v>
+        <v>14247435</v>
       </c>
       <c r="B51" t="n">
-        <v>57649</v>
+        <v>5495</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100110</v>
+        <v>101410</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Rivarliden,Lögdeälven, Ång</t>
+          <t>14 km VSV om Öreström, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>684452</v>
+        <v>683959</v>
       </c>
       <c r="R51" t="n">
-        <v>7104071</v>
+        <v>7105861</v>
       </c>
       <c r="S51" t="n">
-        <v>270</v>
+        <v>100</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6267,22 +6245,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2006-05-20</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2005-08-29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2006-05-20</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2005-08-29</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6297,64 +6265,63 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Per-Olof Nilsson</t>
+          <t>Sveaskog Västerbotten</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Per-Olof Nilsson</t>
+          <t>Via Sveaskog Västerbotten</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>34553059</v>
+        <v>111769654</v>
       </c>
       <c r="B52" t="n">
-        <v>57657</v>
+        <v>90691</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6276</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Korsning mellan väg 92 och Trestenavägen, Ång</t>
+          <t>Paradiset, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>684815</v>
+        <v>684522</v>
       </c>
       <c r="R52" t="n">
-        <v>7102976</v>
+        <v>7103109</v>
       </c>
       <c r="S52" t="n">
-        <v>270</v>
+        <v>50</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6378,27 +6345,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2005-08-29</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2005-08-29</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6407,85 +6359,67 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>kristina stenmarck, Andreas Öster</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>61964236</v>
+        <v>1987249</v>
       </c>
       <c r="B53" t="n">
-        <v>56849</v>
+        <v>80432</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Grusstig, Trolltjärnen, öster om Fredrika, Trolltjärnen, Käringbergets Ekopark, Ång</t>
+          <t>14,1 km VSV om Provåker, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>684547</v>
+        <v>684503</v>
       </c>
       <c r="R53" t="n">
-        <v>7102992</v>
+        <v>7103461</v>
       </c>
       <c r="S53" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6509,12 +6443,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2016-10-13</t>
+          <t>2005-06-04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2016-10-13</t>
+          <t>2005-06-04</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6529,69 +6463,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Raul Vicente</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Raul Vicente</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>70358834</v>
+        <v>1992020</v>
       </c>
       <c r="B54" t="n">
-        <v>79047</v>
+        <v>80432</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>637</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
+          <t>13,8 km VSV om Provåker, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>683258</v>
+        <v>684795</v>
       </c>
       <c r="R54" t="n">
-        <v>7106482</v>
+        <v>7103664</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6615,12 +6540,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2005-08-15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2005-08-15</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6631,44 +6556,26 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>23724142</v>
+        <v>94726893</v>
       </c>
       <c r="B55" t="n">
-        <v>58162</v>
+        <v>80432</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6676,21 +6583,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102995</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6700,17 +6607,17 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Rivarliden,Lögdeälven, Ång</t>
+          <t>Karlsbäck, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>684452</v>
+        <v>684890</v>
       </c>
       <c r="R55" t="n">
-        <v>7104071</v>
+        <v>7103649</v>
       </c>
       <c r="S55" t="n">
-        <v>270</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6734,22 +6641,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2006-05-20</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2021-05-05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2006-05-20</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs inventering.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6764,69 +6666,64 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Per-Olof Nilsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Per-Olof Nilsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>70358842</v>
+        <v>34553059</v>
       </c>
       <c r="B56" t="n">
-        <v>79047</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>637</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
+          <t>Korsning mellan väg 92 och Trestenavägen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>683284</v>
+        <v>684815</v>
       </c>
       <c r="R56" t="n">
-        <v>7106458</v>
+        <v>7102976</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>270</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6850,12 +6747,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2005-08-29</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2005-08-29</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6866,87 +6778,80 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Sveaskog Västerbotten</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Via Sveaskog Västerbotten</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>84302328</v>
+        <v>61964236</v>
       </c>
       <c r="B57" t="n">
-        <v>57654</v>
+        <v>57141</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ormaggan, Stor-Lögdeåberget, Ång</t>
+          <t>Grusstig, Trolltjärnen, öster om Fredrika, Trolltjärnen, Käringbergets Ekopark, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>683554</v>
+        <v>684547</v>
       </c>
       <c r="R57" t="n">
-        <v>7106142</v>
+        <v>7102992</v>
       </c>
       <c r="S57" t="n">
         <v>100</v>
@@ -6973,22 +6878,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2020-04-10</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2016-10-13</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2020-04-10</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2016-10-13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7003,60 +6898,68 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Antoine Bos</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Antoine Bos, Andreas Bernhold</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>103410782</v>
+        <v>111769576</v>
       </c>
       <c r="B58" t="n">
-        <v>92547</v>
+        <v>58057</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4366</v>
+        <v>103031</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Karlsbäck, Ång</t>
+          <t>Paradiset, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>683860</v>
+        <v>684427</v>
       </c>
       <c r="R58" t="n">
-        <v>7105273</v>
+        <v>7103283</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7080,17 +6983,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7105,60 +7003,68 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
+          <t>kristina stenmarck, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>267353</v>
+        <v>20638959</v>
       </c>
       <c r="B59" t="n">
-        <v>79012</v>
+        <v>57950</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>14 km VSV om Öreström, Ång</t>
+          <t>Rivarliden,Lögdeälven, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>683785</v>
+        <v>684452</v>
       </c>
       <c r="R59" t="n">
-        <v>7105048</v>
+        <v>7104071</v>
       </c>
       <c r="S59" t="n">
-        <v>100</v>
+        <v>270</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7182,12 +7088,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2005-07-03</t>
+          <t>2005-04-08</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2005-07-03</t>
+          <t>2005-04-08</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7202,44 +7118,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Per-Olof Nilsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Per-Olof Nilsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>70358828</v>
+        <v>23723936</v>
       </c>
       <c r="B60" t="n">
-        <v>79047</v>
+        <v>57945</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>637</v>
+        <v>100110</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7247,24 +7163,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>bålar</t>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
+          <t>Rivarliden,Lögdeälven, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>683280</v>
+        <v>684452</v>
       </c>
       <c r="R60" t="n">
-        <v>7106483</v>
+        <v>7104071</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>270</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7288,12 +7204,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2006-05-20</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2006-05-20</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7304,82 +7230,73 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN60" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Per-Olof Nilsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Per-Olof Nilsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>84766747</v>
+        <v>20771767</v>
       </c>
       <c r="B61" t="n">
-        <v>79047</v>
+        <v>57141</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>637</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lögdeälven, 5 km uppströms väg 92, Ång</t>
+          <t>Rivarliden,Lögdeälven, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>683262</v>
+        <v>684452</v>
       </c>
       <c r="R61" t="n">
-        <v>7106503</v>
+        <v>7104071</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>270</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7403,12 +7320,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
+          <t>2005-05-08</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
+          <t>2005-05-08</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7423,69 +7350,64 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Per-Olof Nilsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson, Aron Dynesius</t>
+          <t>Per-Olof Nilsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>70358830</v>
+        <v>23724207</v>
       </c>
       <c r="B62" t="n">
-        <v>79047</v>
+        <v>57942</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>637</v>
+        <v>102119</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
+          <t>Rivarliden,Lögdeälven, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>683265</v>
+        <v>684452</v>
       </c>
       <c r="R62" t="n">
-        <v>7106482</v>
+        <v>7104071</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>270</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7509,12 +7431,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2006-05-20</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2006-05-20</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7525,61 +7457,43 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Picea abies</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Per-Olof Nilsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Per-Olof Nilsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>48755363</v>
+        <v>20648541</v>
       </c>
       <c r="B63" t="n">
-        <v>56840</v>
+        <v>57144</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>102612</v>
+        <v>102613</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7589,24 +7503,19 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Ormaggan, Käringbergets Ekopark, Ång</t>
+          <t>Rivarliden,Lögdeälven, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>683438</v>
+        <v>684452</v>
       </c>
       <c r="R63" t="n">
-        <v>7105998</v>
+        <v>7104071</v>
       </c>
       <c r="S63" t="n">
         <v>270</v>
@@ -7633,22 +7542,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2014-03-23</t>
+          <t>2005-04-08</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2014-03-23</t>
+          <t>2005-04-08</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7663,22 +7572,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Sven Jägbrant</t>
+          <t>Per-Olof Nilsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Sven Jägbrant, Jacob Rudhe, André Ahlberg, Isak Vahlström</t>
+          <t>Per-Olof Nilsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>267369</v>
+        <v>23724050</v>
       </c>
       <c r="B64" t="n">
-        <v>79012</v>
+        <v>57364</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7686,37 +7595,41 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>102954</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>15 km V om Öreström, Ång</t>
+          <t>Rivarliden,Lögdeälven, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>683124</v>
+        <v>684452</v>
       </c>
       <c r="R64" t="n">
-        <v>7106553</v>
+        <v>7104071</v>
       </c>
       <c r="S64" t="n">
-        <v>100</v>
+        <v>270</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7740,12 +7653,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2005-07-09</t>
+          <t>2006-05-20</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2005-07-09</t>
+          <t>2006-05-20</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7760,39 +7683,39 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Per-Olof Nilsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Per-Olof Nilsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>20638959</v>
+        <v>23724142</v>
       </c>
       <c r="B65" t="n">
-        <v>57654</v>
+        <v>58463</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>102995</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7841,22 +7764,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2005-04-08</t>
+          <t>2006-05-20</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2005-04-08</t>
+          <t>2006-05-20</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7883,10 +7806,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>20648541</v>
+        <v>26289615</v>
       </c>
       <c r="B66" t="n">
-        <v>56852</v>
+        <v>58636</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7894,16 +7817,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>102613</v>
+        <v>103044</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7913,7 +7836,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7952,22 +7880,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2005-04-08</t>
+          <t>2007-05-27</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2005-04-08</t>
+          <t>2007-05-27</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7987,55 +7915,55 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Per-Olof Nilsson</t>
+          <t>Per-Olof Nilsson, Stefan Delin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>84766751</v>
+        <v>378079</v>
       </c>
       <c r="B67" t="n">
-        <v>79047</v>
+        <v>92369</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>637</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lögdeälven, 5 km uppströms väg 92, Ång</t>
+          <t>13,7 km VSV om Provåker, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>683264</v>
+        <v>685169</v>
       </c>
       <c r="R67" t="n">
-        <v>7106487</v>
+        <v>7102592</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8059,12 +7987,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
+          <t>2005-06-13</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
+          <t>2005-06-13</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8079,430 +8007,15 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson, Aron Dynesius</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>85601</v>
-      </c>
-      <c r="B68" t="n">
-        <v>96614</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>53</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Crossocalyx hellerianus</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>14 km V om Öreström, Ång</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>683893</v>
-      </c>
-      <c r="R68" t="n">
-        <v>7106501</v>
-      </c>
-      <c r="S68" t="n">
-        <v>100</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>2005-06-16</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2005-06-16</t>
-        </is>
-      </c>
-      <c r="AD68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT68" t="inlineStr"/>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>Sveaskog Västerbotten</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>Via Sveaskog Västerbotten</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>266906</v>
-      </c>
-      <c r="B69" t="n">
-        <v>79012</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>185</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Violettgrå tagellav</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Bryoria nadvornikiana</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>14 km SV om Västra Örtträsk, Ång</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>682187</v>
-      </c>
-      <c r="R69" t="n">
-        <v>7107831</v>
-      </c>
-      <c r="S69" t="n">
-        <v>100</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2005-06-29</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2005-06-29</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Sveaskog Västerbotten</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Via Sveaskog Västerbotten</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>1992020</v>
-      </c>
-      <c r="B70" t="n">
-        <v>80083</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>13,8 km VSV om Provåker, Ång</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>684795</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7103664</v>
-      </c>
-      <c r="S70" t="n">
-        <v>100</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2005-08-15</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2005-08-15</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Sveaskog Västerbotten</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Via Sveaskog Västerbotten</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70358823</v>
-      </c>
-      <c r="B71" t="n">
-        <v>79047</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>637</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Ringlav</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Evernia divaricata</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Lögdeälven 5 km uppströms väg 92, Ång</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>683272</v>
-      </c>
-      <c r="R71" t="n">
-        <v>7106494</v>
-      </c>
-      <c r="S71" t="n">
-        <v>10</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2018-04-03</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2018-04-03</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN71" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
